--- a/www/download/IND.capital_stock.s.us.rpPE.xlsx
+++ b/www/download/IND.capital_stock.s.us.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>1538087.02899907</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1590164.74926371</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1500355.89328043</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.283</t>
+          <t>1283312.26438895</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.331</t>
+          <t>1330856.39715423</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1269664.39282344</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>1132604.27923937</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>1202551.23465361</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1469065.97468466</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.727</t>
+          <t>1726600.80144075</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>1855848.27386571</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.907</t>
+          <t>1907051.14573615</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2.169</t>
+          <t>2169376.54425187</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>2388624.46234074</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>2294004.94937459</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,67 +775,67 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>858090.456761757</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>847096.229715934</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>762889.330515573</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>771212.170255622</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>752101.804375487</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>681310.690461719</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>676495.154287948</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>728771.629948285</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>888093.606229298</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1000256.00286859</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1027107.91024614</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>1071058.63251297</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>1216284.32354166</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -847,7 +852,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>856723.160922217</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>843663.633211832</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>758561.906929261</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>779376.667471995</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>783058.218019589</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>715560.663943996</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>718025.400210937</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>774142.33641661</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.959</t>
+          <t>959426.798719664</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1117434.49111651</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.179</t>
+          <t>1178579.94687948</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>1273352.67021226</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.477</t>
+          <t>1476781.63982967</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1691948.83062529</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1618600.58645843</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>59355.9918630032</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69181.360625382</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57565.0534638733</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57282.9470666745</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56099.0221085957</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>49644.40832393</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51815.9310363921</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>56629.2617187464</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69005.7104614056</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81828.1596914803</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>94664.9996971436</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108329.971368739</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>134829.532811473</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171064.196342325</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>169178.186375985</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.658</t>
+          <t>2657544.91490704</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.755</t>
+          <t>2754537.28489732</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.787</t>
+          <t>2787196.46883731</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.719</t>
+          <t>2718929.34610389</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>1895367.49971133</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>2115917.71359179</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.834</t>
+          <t>1833706.71262236</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>1768386.41775049</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>1809238.63981075</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2.085</t>
+          <t>2085356.56153879</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2.611</t>
+          <t>2610569.13966916</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2.933</t>
+          <t>2933384.85080145</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>3542955.74900728</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.244</t>
+          <t>4243999.76630099</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>4227866.28044271</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.806</t>
+          <t>1806419.95744152</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.904</t>
+          <t>1903619.63119832</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>1991378.04293049</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.974</t>
+          <t>1974309.49369325</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2102640.56365441</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>2247626.8056084</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.293</t>
+          <t>2293100.26203844</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.404</t>
+          <t>2404134.85737192</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.882</t>
+          <t>2881662.72184117</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3.334</t>
+          <t>3334460.74685826</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3.792</t>
+          <t>3792269.76059826</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4.335</t>
+          <t>4335280.5429461</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>4.913</t>
+          <t>4912526.2304056</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>5.281</t>
+          <t>5281158.21733246</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>5149659.56775567</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.127</t>
+          <t>2126558.60724414</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.361</t>
+          <t>2361413.11970726</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.489</t>
+          <t>2488756.12919788</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>2578115.65116243</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>2704997.60990416</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.815</t>
+          <t>2815277.64064881</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.982</t>
+          <t>2981608.22690928</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.159</t>
+          <t>3158527.52731261</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3439734.60767454</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3.875</t>
+          <t>3874822.31367192</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>4348902.36244183</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>4.881</t>
+          <t>4880878.19600143</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5.606</t>
+          <t>5606362.67948541</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7.133</t>
+          <t>7132996.54979171</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>7059783.82168639</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,72 +1297,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36529.8037857805</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37487.7032509869</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35563.213394576</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36751.9667967827</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>36265.9523848064</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32633.2348156165</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33016.6545840697</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36533.9452894855</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45002.8512596556</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53359.7893934907</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57946.9071727335</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62627.0932247143</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72474.0691091171</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>86099.5392394877</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1369,7 +1374,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,67 +1384,67 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>245498.944834045</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>262404.984455268</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>246863.545920945</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251535.982032188</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232354.061230121</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>217074.06555197</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>227769.80376059</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>266309.526907654</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>310306.857222978</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>356175.937376202</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>389305.140198336</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>418461.297431486</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>480946.802273826</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1456,7 +1461,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,67 +1471,67 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8.512</t>
+          <t>8511749.96256924</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.276</t>
+          <t>8276300.33663781</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.367</t>
+          <t>7366901.39568792</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7.401</t>
+          <t>7401377.1805815</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.184</t>
+          <t>7184357.139993</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>6412025.09902104</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.311</t>
+          <t>6310558.6501231</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.739</t>
+          <t>6738992.81156657</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8.105</t>
+          <t>8104710.03110398</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.144</t>
+          <t>9144246.35647392</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>9.183</t>
+          <t>9183339.8407178</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>9.438</t>
+          <t>9437534.09870476</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.884</t>
+          <t>10884321.7521092</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1543,7 +1548,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,67 +1558,67 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.715</t>
+          <t>715381.910500846</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>709772.477686175</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>632367.628214615</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.632</t>
+          <t>631824.896483757</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>617201.332464887</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550681.842535283</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545429.626777945</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>579962.246506701</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>696232.369591542</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>776989.753922345</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>806714.107145036</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>826951.669697429</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>937322.41144249</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1630,7 +1635,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,67 +1645,67 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>2112166.5018118</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>2180500.62823819</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>1985902.06707059</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2.035</t>
+          <t>2034912.54597896</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.095</t>
+          <t>2095213.63527716</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.023</t>
+          <t>2022897.09422545</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>2118527.5765778</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.449</t>
+          <t>2449366.85224449</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.214</t>
+          <t>3213887.97397246</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3.893</t>
+          <t>3892532.23570367</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4.255</t>
+          <t>4254845.27958112</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>4.685</t>
+          <t>4684517.58514539</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>5.504</t>
+          <t>5503591.05807592</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1717,7 +1722,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15075.3469067108</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16688.5233172253</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16250.6814097098</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17142.8042501008</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17576.1241710507</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>16366.7523337209</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17744.8560943062</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>20493.0261604917</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26825.4155126232</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32943.4903503841</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>37326.934013361</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45488.4342718116</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>58978.9093797376</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>66640.7588690546</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62017.4964204802</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,67 +1819,67 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>434990.525963539</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>412643.00441802</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>381606.223665989</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>388762.780515372</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389772.201027538</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>364000.321458247</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>383057.173530358</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>407346.842208847</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>492317.157588525</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>560784.573433505</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.593</t>
+          <t>592896.670205935</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>630188.406590516</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>734524.414821197</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1891,7 +1896,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,67 +1906,67 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.606</t>
+          <t>6606237.27834427</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.597</t>
+          <t>6597440.64278686</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.931</t>
+          <t>5931238.33417218</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5.983</t>
+          <t>5983081.67530815</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.843</t>
+          <t>5842802.91696989</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.252</t>
+          <t>5252449.91704269</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.273</t>
+          <t>5273150.96433174</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.791</t>
+          <t>5790693.10374269</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7.146</t>
+          <t>7146351.84054792</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>8.308</t>
+          <t>8307578.21901045</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>8.753</t>
+          <t>8753350.30678464</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9.475</t>
+          <t>9475332.64547453</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>10.893</t>
+          <t>10892653.4373844</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1978,7 +1983,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,67 +1993,67 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>2763663.07938533</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.874</t>
+          <t>2874492.27388289</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.104</t>
+          <t>3103675.08207785</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3.286</t>
+          <t>3285574.5211948</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>3373543.96830096</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>3316084.58972</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3249801.39741351</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.579</t>
+          <t>3578671.50054565</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>4115301.26386587</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4.905</t>
+          <t>4904674.42694353</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>5124591.48593073</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>5.395</t>
+          <t>5394953.78242375</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>6.298</t>
+          <t>6297565.08436557</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2065,7 +2070,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>335225.885817694</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>356932.075473853</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>346539.195742387</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>352321.394300357</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.369</t>
+          <t>368559.8096196</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>340139.918760941</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>351157.720698932</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>397789.440595074</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>515373.910056097</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>607139.36665598</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>646730.500102854</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>703683.416354248</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>824697.360216687</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.951</t>
+          <t>950797.044925546</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>926219.70721984</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,67 +2167,67 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>254508.305141285</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>249505.11536862</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>236307.741572287</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>218297.248732917</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>215051.488527582</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>194374.693144571</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>201827.141007188</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239499.926519695</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.287</t>
+          <t>286938.955093062</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339376.053194343</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>361040.650152018</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>364782.048612521</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>430985.282906479</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2239,7 +2244,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>565338.501762948</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>621007.901438404</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>571610.639337541</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>328153.034567267</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>473266.443877202</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>471412.635755221</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.438</t>
+          <t>438062.393574817</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>508414.653859651</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>618407.651877284</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>662623.014564901</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>711488.528704662</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>964991.64240088</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1116617.31158432</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.304</t>
+          <t>1303614.24898626</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>1368202.98621071</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>843277.635398844</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>876969.433422282</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>942357.87911787</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>916608.381659981</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>958236.780478598</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1022074.4888626</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1089764.88600799</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1159366.17728751</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>1337197.4616402</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1579909.15284148</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>1842048.50694835</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>2075769.18525513</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2.659</t>
+          <t>2658636.57804784</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2.948</t>
+          <t>2948367.05553636</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2990188.09248265</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,67 +2428,67 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>165791.087053843</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>178033.329237241</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>181733.881635705</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185067.896370213</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>186982.497140142</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177753.198114959</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>184456.723820911</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>207323.147820766</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>272207.674054964</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>329071.438269788</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>370978.698109013</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>435573.725423319</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>549546.964525575</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2500,7 +2505,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,67 +2515,67 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.926</t>
+          <t>3926439.23683898</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.313</t>
+          <t>4312841.93526092</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4.051</t>
+          <t>4051046.55166359</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>4085394.52495392</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3.956</t>
+          <t>3956020.15316128</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.539</t>
+          <t>3539065.09857788</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>3533085.32234121</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3.901</t>
+          <t>3900647.95463223</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4.834</t>
+          <t>4834248.85836636</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>5510229.03828239</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>5.693</t>
+          <t>5693345.01691844</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5.919</t>
+          <t>5918710.30586855</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>6.729</t>
+          <t>6729429.19981627</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2587,7 +2592,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21.289</t>
+          <t>21289271.5883617</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18.315</t>
+          <t>18315178.6879104</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.234</t>
+          <t>16233901.8565931</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14.762</t>
+          <t>14761559.2202773</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>16.629</t>
+          <t>16628739.7894945</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17.17</t>
+          <t>17169878.1278504</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14.986</t>
+          <t>14986316.6725713</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14.368</t>
+          <t>14367934.1551703</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>15.445</t>
+          <t>15445118.637219</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>16.527</t>
+          <t>16527248.3586938</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>16.431</t>
+          <t>16431446.4708916</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>15.696</t>
+          <t>15695785.5143952</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>15.67</t>
+          <t>15670296.4921833</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>18.261</t>
+          <t>18261131.6571798</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>19.296</t>
+          <t>19296059.8571648</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>1760829.1189605</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>1877338.60876306</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.816</t>
+          <t>1815958.90185428</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1.339</t>
+          <t>1339132.81334857</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>1562163.15089374</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.701</t>
+          <t>1701353.49363953</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.595</t>
+          <t>1594994.15101507</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1798851.73688326</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2.104</t>
+          <t>2103913.66621226</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2.357</t>
+          <t>2357180.08736089</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2.795</t>
+          <t>2795229.38105993</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>3.142</t>
+          <t>3142233.58718998</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3.441</t>
+          <t>3440728.34002697</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3.361</t>
+          <t>3360863.6263319</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3.066</t>
+          <t>3066435.03210023</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24600.7898997101</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27546.6244373116</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>30603.485199467</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31813.1379045267</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>32026.7029437954</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32640.4917139336</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>33887.0412155523</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37548.8012106701</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>47207.3276034981</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55893.2189614342</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>62765.6060762895</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72359.252719093</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>93978.2073332064</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>115669.457151328</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>102329.524978285</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>73909.4002712656</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72364.9433489986</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>65264.9123476706</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66189.5568281788</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>66293.7003841872</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>60799.2398683111</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62437.8824717733</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68342.0313112152</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>84565.0969959058</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95992.5687797753</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>103732.684074704</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107404.514445848</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123173.684150599</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140071.92969083</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>133436.289238144</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15264.8048315482</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18050.3989317155</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17947.6371834533</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18348.5717083518</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20587.7991936461</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22089.2165873931</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22571.0565475078</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>22606.0018448414</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>26250.0880714291</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>31645.6417443656</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36512.6535803401</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>45847.9839831326</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69852.39447318</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88187.4801613657</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>80206.6576789869</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>1392977.02608068</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.549</t>
+          <t>1548501.44712286</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.808</t>
+          <t>1808213.20335516</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>1933958.79146245</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.096</t>
+          <t>2095563.84921221</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.383</t>
+          <t>2383132.17813454</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.475</t>
+          <t>2474514.0051568</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.383</t>
+          <t>2382793.95028379</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2219608.77279353</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.315</t>
+          <t>2314927.23322411</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.474</t>
+          <t>2474490.05602413</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.639</t>
+          <t>2639359.39218072</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.751</t>
+          <t>2751211.1014522</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.943</t>
+          <t>2943006.74161748</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.608</t>
+          <t>2608367.60808784</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10387.5856369219</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10472.6167481845</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>9483.38162869941</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10201.0690177384</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10220.2398503971</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10254.1775437209</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10625.9934267763</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11585.0704704321</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13726.6270515646</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15507.6288577581</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15925.640501504</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>17769.8778930057</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>21012.7662506392</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24984.4029645788</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24997.3651176415</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,67 +3211,67 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>1496157.71432994</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>1478277.10103172</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1317570.51764548</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1344462.34031398</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1343875.25775235</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>1236786.42357057</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1268976.89371771</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1386250.90826854</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1.721</t>
+          <t>1720549.65296268</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.941</t>
+          <t>1941061.64441195</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>1.998</t>
+          <t>1997579.77597407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>2106550.71809876</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>2389477.35353878</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3283,7 +3288,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,67 +3298,67 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>426619.898502123</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>464177.552923918</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>452635.807269903</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>494548.346133708</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>480450.148587969</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>486745.455241911</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>539597.482887317</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>553798.994567247</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>601526.101635378</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>671938.500413658</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>785564.806423376</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>855912.421604851</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>1042806.03475039</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3370,7 +3375,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,72 +3385,72 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>252503.423695737</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>265446.736551503</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.251</t>
+          <t>251036.482845167</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259161.331950268</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>264984.097880274</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>256637.933778636</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>266276.129359737</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>303086.861468923</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377851.644004267</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>441580.44506998</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>464635.182431894</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>549246.397136294</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>635663.922809273</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>748501.928456876</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3457,7 +3462,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134405.670555828</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138291.398437762</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128341.58407335</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140767.682605421</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125102.10611178</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>131661.510884344</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>143033.378187658</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>157317.857442779</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>193740.910292466</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>232061.861481868</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>297438.897168626</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>348189.400856234</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>469596.611271851</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>558820.926701643</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>489307.462464804</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>698398.796653517</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1060610.45048632</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1109586.31399928</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>988657.354094549</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>495139.533299384</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>649222.023518284</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>753625.211715742</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>820040.265349154</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>946943.80952797</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.215</t>
+          <t>1214773.63670156</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.466</t>
+          <t>1466044.81210744</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.796</t>
+          <t>1795955.24022668</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.368</t>
+          <t>2368231.30818118</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>3.122</t>
+          <t>3122145.92713759</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2.751</t>
+          <t>2751483.29982883</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>67974.0340237687</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76089.0821652557</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76225.1820023043</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>81488.688512532</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74666.3660914128</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75271.0594799448</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78839.4587108452</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90809.7029054219</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117715.378261412</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>142386.934915846</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158701.616501227</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>176099.21354047</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>224127.269080553</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>275751.31612799</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>271426.315121503</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42389.9215887585</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>42892.9633015573</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>41831.5572499992</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>45361.851554707</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46489.8323809797</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>43248.2268829437</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>44081.1831907078</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>48971.3232784494</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62434.2065509712</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75315.7892697419</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81725.3394066407</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88550.1288689718</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>107022.898406523</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>134173.403031698</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98881.1982173894</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,67 +3820,67 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>545298.549566519</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>595671.882688816</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>546296.317448332</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>550559.584078313</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>559827.924355327</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>546059.288310521</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>516590.591712231</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>572674.271663728</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>700425.904121031</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>789646.203294406</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>808590.697184944</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>855373.532513009</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>985730.606451543</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3892,7 +3897,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.499</t>
+          <t>499474.418550874</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>533756.468206192</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>550437.999649289</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>587776.21452127</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>559877.827440956</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>582562.337127349</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>490054.966676935</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>493727.862124982</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>595800.201780415</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>745855.383845791</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>850453.953280078</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>967933.017182874</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>1.129</t>
+          <t>1128625.07103967</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>1439376.87839401</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>1175142.74268913</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>504927.311922058</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>516427.067409121</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>538741.153781766</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>517485.758141669</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.576</t>
+          <t>575972.257501595</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>634283.138830458</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.603</t>
+          <t>603069.804562106</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>612526.70345318</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.655</t>
+          <t>655216.869322225</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>761752.847290309</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.817</t>
+          <t>817496.487232387</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>872795.86096111</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>930138.657206178</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>1.064</t>
+          <t>1064420.98925107</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>1002614.26620783</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>18.821</t>
+          <t>18820738.7267015</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19.468</t>
+          <t>19467731.1849622</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>20100491.6054108</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20.583</t>
+          <t>20582893.4693189</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21.128</t>
+          <t>21128069.7648515</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>22.081</t>
+          <t>22081105.0672071</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>23.016</t>
+          <t>23016105.2719886</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>23.567</t>
+          <t>23566756.2963514</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>24.422</t>
+          <t>24422075.8107447</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>26.072</t>
+          <t>26071712.8527379</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>27.759</t>
+          <t>27759307.9911121</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>28.717</t>
+          <t>28717271.640767</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>28.562</t>
+          <t>28562155.6013977</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>29.835</t>
+          <t>29834682.0875331</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>29.951</t>
+          <t>29950773.6097914</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>11.287</t>
+          <t>11287271.9902858</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11.943</t>
+          <t>11942508.9348878</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11.946</t>
+          <t>11945918.5933329</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>11.365</t>
+          <t>11364521.3171774</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>11.408</t>
+          <t>11407697.1526909</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>11.324</t>
+          <t>11324336.6067459</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11.035</t>
+          <t>11034687.812736</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>10.701</t>
+          <t>10701325.7988415</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>11.762</t>
+          <t>11762000.0633527</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>13.123</t>
+          <t>13123295.6721036</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>14.756</t>
+          <t>14755636.6807407</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>16.116</t>
+          <t>16116254.6275372</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>18.165</t>
+          <t>18165154.8461758</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>16.479</t>
+          <t>16479061.5746225</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>15.662</t>
+          <t>15662341.9588696</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>96.778</t>
+          <t>96778054.8946727</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>96.784</t>
+          <t>96784030.5238092</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>93.417</t>
+          <t>93417153.378709</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>91.398</t>
+          <t>91398232.472819</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>93.05</t>
+          <t>93050073.1204685</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>93.252</t>
+          <t>93252101.2622381</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>91.585</t>
+          <t>91585051.8448396</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>94.372</t>
+          <t>94371503.0139495</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>105.628</t>
+          <t>105628209.099678</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>117.888</t>
+          <t>117888168.432761</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>125.897</t>
+          <t>125897169.697855</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>133.12</t>
+          <t>133119793.668559</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>146.41</t>
+          <t>146410390.501571</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>104.856</t>
+          <t>104856160.996644</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>102.58</t>
+          <t>102579524.861984</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>capital_stock.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
